--- a/Exercícios/SigTransp.xlsx
+++ b/Exercícios/SigTransp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\4. Projetos TIC - Química\ptic_quimica\Exercícios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7515503E-3784-41D1-B2C8-F09882E5AF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64949BCA-6885-4813-B92D-5ADF77D3C830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
@@ -139,9 +139,6 @@
     <t>Média de custos</t>
   </si>
   <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
     <t>Prazo (dias úteis)</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>Velocidade média</t>
   </si>
   <si>
-    <t>Custos totais</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
@@ -179,6 +173,12 @@
   </si>
   <si>
     <t>Tempo detalhado</t>
+  </si>
+  <si>
+    <t>Custos totais (Soma dos custos)</t>
+  </si>
+  <si>
+    <t>Faturamento (Total de fretes)</t>
   </si>
 </sst>
 </file>
@@ -189,7 +189,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -274,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -419,20 +419,54 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
-        <color rgb="FFFF0000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FFFF0000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -441,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -461,15 +495,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -488,28 +513,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -518,57 +561,38 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -982,409 +1006,409 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="42" t="str">
+        <f ca="1">"Hoje é "&amp;TEXT(NOW(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa"". Horário: ""hh:mm:ss")</f>
+        <v>Hoje é segunda-feira, dia 11 de maio de 2026. Horário: 20:27:41</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="43">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="L2" s="39">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="27" t="str">
-        <f ca="1">"Hoje é "&amp;TEXT(NOW(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa"". Horário: ""hh:mm:ss")</f>
-        <v>Hoje é segunda-feira, dia 11 de maio de 2026. Horário: 19:50:47</v>
-      </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="13">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="L2" s="12">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="H3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="37" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="17">
+      <c r="B4" s="14">
         <v>45286</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="14">
         <v>45296</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="15">
         <f>C4-B4</f>
         <v>10</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="15" t="str">
+      <c r="F4" s="12" t="str">
         <f>RIGHT(E4,2)</f>
         <v>MG</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="12">
         <v>1187</v>
       </c>
-      <c r="H4" s="49">
+      <c r="H4" s="21">
         <f>G4/$L$2</f>
         <v>14.8375</v>
       </c>
-      <c r="I4" s="15" t="str">
+      <c r="I4" s="12" t="str">
         <f>TEXT(H4/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos""")</f>
         <v>00 dias, 14 hora(s), 50 minuto(s), 15 segundos</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="17">
         <v>2686.67</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="17">
         <v>7793.19</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17">
+      <c r="B5" s="14">
         <v>45286</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>45293</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="15">
         <f>C5-B5</f>
         <v>7</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="15" t="str">
+      <c r="F5" s="12" t="str">
         <f>RIGHT(E5,2)</f>
         <v>SP</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="12">
         <v>587</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="21">
         <f t="shared" ref="H5:H12" si="0">G5/$L$2</f>
         <v>7.3375000000000004</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="19" t="s">
+      <c r="I5" s="12"/>
+      <c r="J5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="18">
         <v>1787.03</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="18">
         <v>4116.8500000000004</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>45289</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <v>45310</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="15">
         <f t="shared" ref="D6:D12" si="1">C6-B6</f>
         <v>21</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="15" t="str">
+      <c r="F6" s="12" t="str">
         <f t="shared" ref="F6:F12" si="2">RIGHT(E6,2)</f>
         <v>PR</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="12">
         <v>1457</v>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="21">
         <f t="shared" si="0"/>
         <v>18.212499999999999</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="19" t="s">
+      <c r="I6" s="12"/>
+      <c r="J6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="18">
         <v>3537.57</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="18">
         <v>9446.19</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17">
+      <c r="B7" s="14">
         <v>45293</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>45317</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="15">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="15" t="str">
+      <c r="F7" s="12" t="str">
         <f t="shared" si="2"/>
         <v>GO</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="12">
         <v>1052</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="21">
         <f t="shared" si="0"/>
         <v>13.15</v>
       </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="12"/>
+      <c r="J7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="18">
         <v>1976.18</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="18">
         <v>6966.1</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17">
+      <c r="B8" s="14">
         <v>45302</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="14">
         <v>45351</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="15">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="15" t="str">
+      <c r="F8" s="12" t="str">
         <f t="shared" si="2"/>
         <v>RS</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>2909</v>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="21">
         <f t="shared" si="0"/>
         <v>36.362499999999997</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="19" t="s">
+      <c r="I8" s="12"/>
+      <c r="J8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="18">
         <v>6094.88</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="18">
         <v>18343.55</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17">
+      <c r="B9" s="14">
         <v>45303</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>45356</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="15">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="str">
+      <c r="F9" s="12" t="str">
         <f t="shared" si="2"/>
         <v>PE</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="12">
         <v>5013</v>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="21">
         <f t="shared" si="0"/>
         <v>62.662500000000001</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="19" t="s">
+      <c r="I9" s="12"/>
+      <c r="J9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="18">
         <v>8389.85</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="18">
         <v>31228.11</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17">
+      <c r="B10" s="14">
         <v>45289</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="14">
         <v>45309</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="15">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="15" t="str">
+      <c r="F10" s="12" t="str">
         <f t="shared" si="2"/>
         <v>RJ</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="12">
         <v>1585</v>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="21">
         <f t="shared" si="0"/>
         <v>19.8125</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="19" t="s">
+      <c r="I10" s="12"/>
+      <c r="J10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="18">
         <v>4363.38</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="18">
         <v>10234.4</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <v>45301</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>45344</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="15">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="15" t="str">
+      <c r="F11" s="12" t="str">
         <f t="shared" si="2"/>
         <v>BA</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="12">
         <v>3664</v>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="21">
         <f t="shared" si="0"/>
         <v>45.8</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="19" t="s">
+      <c r="I11" s="12"/>
+      <c r="J11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="18">
         <v>6500.36</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="18">
         <v>22963.33</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17">
+      <c r="B12" s="14">
         <v>45302</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="14">
         <v>45349</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="15">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="15" t="str">
+      <c r="F12" s="12" t="str">
         <f t="shared" si="2"/>
         <v>SP</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="12">
         <v>799</v>
       </c>
-      <c r="H12" s="49">
+      <c r="H12" s="21">
         <f t="shared" si="0"/>
         <v>9.9875000000000007</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="19" t="s">
+      <c r="I12" s="12"/>
+      <c r="J12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="18">
         <v>2406.79</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="18">
         <v>5415.77</v>
       </c>
     </row>
@@ -1393,226 +1417,111 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="38"/>
+      <c r="C14" s="34"/>
       <c r="E14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="29"/>
+      <c r="F14" s="19"/>
+      <c r="I14" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="44"/>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="38"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="23"/>
+      <c r="F15" s="20"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="45"/>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="38"/>
+      <c r="C16" s="27"/>
       <c r="E16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+      <c r="F16" s="19"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
     </row>
     <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="38"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="28" t="s">
+      <c r="F17" s="20"/>
+      <c r="I17" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="44"/>
     </row>
     <row r="18" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="23"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="45"/>
     </row>
     <row r="19" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="38"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
+        <v>34</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
     </row>
     <row r="20" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="38"/>
+      <c r="C20" s="27"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="29"/>
+      <c r="F20" s="20"/>
+      <c r="I20" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="44"/>
     </row>
     <row r="21" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="23"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="45"/>
     </row>
     <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="38"/>
+      <c r="C22" s="27"/>
       <c r="E22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="38"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
     </row>
     <row r="24" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="39"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
+      <c r="B26"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33"/>
@@ -1623,7 +1532,12 @@
       <sortCondition ref="E3"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="22">
+  <mergeCells count="16">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="B24:C24"/>
@@ -1632,20 +1546,9 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="H21:J21"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="B1:D2"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{B72A01B5-D524-4E54-83CF-39C6147C2C75}">

--- a/Exercícios/SigTransp.xlsx
+++ b/Exercícios/SigTransp.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\4. Projetos TIC - Química\ptic_quimica\Exercícios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64949BCA-6885-4813-B92D-5ADF77D3C830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E95855-05AF-4451-8987-A842C4D64060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
     <sheet name="Transp" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transp!$B$3:$J$3</definedName>
+    <definedName name="Destinos">Transp!$E$4:$E$17</definedName>
+    <definedName name="Estados">Transp!$F$4:$F$17</definedName>
+    <definedName name="Fretes">Transp!$L$4:$L$17</definedName>
+    <definedName name="Motoristas">Transp!$J$4:$J$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -172,13 +176,19 @@
     <t>Taquaritinga - SP</t>
   </si>
   <si>
-    <t>Tempo detalhado</t>
-  </si>
-  <si>
     <t>Custos totais (Soma dos custos)</t>
   </si>
   <si>
     <t>Faturamento (Total de fretes)</t>
+  </si>
+  <si>
+    <t>Tempo detalhado (Coluna automática - não mexer)</t>
+  </si>
+  <si>
+    <t>=SOMASE(Destinos;B20;Fretes)</t>
+  </si>
+  <si>
+    <t>=MÉDIA(D4:D17)</t>
   </si>
 </sst>
 </file>
@@ -191,7 +201,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,8 +263,29 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,8 +304,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -470,12 +513,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -489,15 +552,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -506,9 +560,6 @@
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -519,41 +570,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -561,37 +597,96 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -989,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
-  <dimension ref="B1:L33"/>
+  <dimension ref="B1:L39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -998,7 +1093,7 @@
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
     <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
@@ -1011,20 +1106,20 @@
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="38" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1032,499 +1127,619 @@
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="42" t="str">
+      <c r="F2" s="29" t="str">
         <f ca="1">"Hoje é "&amp;TEXT(NOW(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa"". Horário: ""hh:mm:ss")</f>
-        <v>Hoje é segunda-feira, dia 11 de maio de 2026. Horário: 20:27:41</v>
-      </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43">
+        <v>Hoje é terça-feira, dia 19 de maio de 2026. Horário: 13:08:23</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="17">
         <v>0.61111111111111116</v>
       </c>
-      <c r="L2" s="39">
-        <v>80</v>
+      <c r="L2" s="15">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7">
+        <v>46365</v>
+      </c>
+      <c r="C4" s="7">
+        <f>B4+6</f>
+        <v>46371</v>
+      </c>
+      <c r="D4" s="49"/>
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="50"/>
+      <c r="G4" s="5">
+        <v>1187</v>
+      </c>
+      <c r="H4" s="51"/>
+      <c r="I4" s="43" t="str">
+        <f>IF(H4&lt;&gt;"",TEXT(H4/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos"""),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="9">
+        <v>2686.67</v>
+      </c>
+      <c r="L4" s="9">
+        <v>7793.19</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7">
+        <v>46339</v>
+      </c>
+      <c r="C5" s="7">
+        <f>B5+7</f>
+        <v>46346</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="50"/>
+      <c r="G5" s="5">
+        <v>587</v>
+      </c>
+      <c r="H5" s="51"/>
+      <c r="I5" s="43" t="str">
+        <f t="shared" ref="I5:I17" si="0">IF(H5&lt;&gt;"",TEXT(H5/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos"""),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1787.03</v>
+      </c>
+      <c r="L5" s="10">
+        <v>4116.8500000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7">
+        <v>46358</v>
+      </c>
+      <c r="C6" s="7">
+        <f>B6+8</f>
+        <v>46366</v>
+      </c>
+      <c r="D6" s="49"/>
+      <c r="E6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="50"/>
+      <c r="G6" s="5">
+        <v>5013</v>
+      </c>
+      <c r="H6" s="51"/>
+      <c r="I6" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="10">
+        <v>8389.85</v>
+      </c>
+      <c r="L6" s="10">
+        <v>31228.11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C7" s="7">
+        <f>B7+9</f>
+        <v>46024</v>
+      </c>
+      <c r="D7" s="49"/>
+      <c r="E7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="50"/>
+      <c r="G7" s="5">
+        <v>1585</v>
+      </c>
+      <c r="H7" s="51"/>
+      <c r="I7" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="10">
+        <v>4363.38</v>
+      </c>
+      <c r="L7" s="10">
+        <v>10234.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C8" s="7">
+        <f>B8+10</f>
+        <v>46177</v>
+      </c>
+      <c r="D8" s="49"/>
+      <c r="E8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="50"/>
+      <c r="G8" s="5">
+        <v>3664</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="10">
+        <v>6500.36</v>
+      </c>
+      <c r="L8" s="10">
+        <v>22963.33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7">
+        <v>46325</v>
+      </c>
+      <c r="C9" s="7">
+        <f>B9+10</f>
+        <v>46335</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="50"/>
+      <c r="G9" s="5">
+        <v>3664</v>
+      </c>
+      <c r="H9" s="51"/>
+      <c r="I9" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="10">
+        <v>6500.36</v>
+      </c>
+      <c r="L9" s="10">
+        <v>22963.33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C10" s="7">
+        <f>B10+9</f>
+        <v>45991</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="50"/>
+      <c r="G10" s="5">
+        <v>799</v>
+      </c>
+      <c r="H10" s="51"/>
+      <c r="I10" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="10">
+        <v>2406.79</v>
+      </c>
+      <c r="L10" s="10">
+        <v>5415.77</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7">
+        <v>45906</v>
+      </c>
+      <c r="C11" s="7">
+        <f>B11+8</f>
+        <v>45914</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="50"/>
+      <c r="G11" s="5">
+        <v>1457</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="10">
+        <v>3537.57</v>
+      </c>
+      <c r="L11" s="10">
+        <v>9446.19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C12" s="7">
+        <f>B12+7</f>
+        <v>45968</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="50"/>
+      <c r="G12" s="5">
+        <v>1052</v>
+      </c>
+      <c r="H12" s="51"/>
+      <c r="I12" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1976.18</v>
+      </c>
+      <c r="L12" s="10">
+        <v>6966.1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7">
+        <v>46166</v>
+      </c>
+      <c r="C13" s="7">
+        <f>B13+6</f>
+        <v>46172</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="50"/>
+      <c r="G13" s="5">
+        <v>2909</v>
+      </c>
+      <c r="H13" s="51"/>
+      <c r="I13" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="10">
+        <v>6094.88</v>
+      </c>
+      <c r="L13" s="10">
+        <v>18343.55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C14" s="7">
+        <f>B14+5</f>
+        <v>46070</v>
+      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="50"/>
+      <c r="G14" s="5">
+        <v>5013</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="10">
+        <v>8389.85</v>
+      </c>
+      <c r="L14" s="10">
+        <v>31228.11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C15" s="7">
+        <f>B15+12</f>
+        <v>45915</v>
+      </c>
+      <c r="D15" s="49"/>
+      <c r="E15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="50"/>
+      <c r="G15" s="5">
+        <v>1585</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="10">
+        <v>4363.38</v>
+      </c>
+      <c r="L15" s="10">
+        <v>10234.4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C16" s="7">
+        <f>B16+11</f>
+        <v>46016</v>
+      </c>
+      <c r="D16" s="49"/>
+      <c r="E16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="50"/>
+      <c r="G16" s="5">
+        <v>3664</v>
+      </c>
+      <c r="H16" s="51"/>
+      <c r="I16" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="10">
+        <v>6500.36</v>
+      </c>
+      <c r="L16" s="10">
+        <v>22963.33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
+        <v>46144</v>
+      </c>
+      <c r="C17" s="7">
+        <f>B17+20</f>
+        <v>46164</v>
+      </c>
+      <c r="D17" s="49"/>
+      <c r="E17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="5">
+        <v>799</v>
+      </c>
+      <c r="H17" s="51"/>
+      <c r="I17" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="10">
+        <v>2406.79</v>
+      </c>
+      <c r="L17" s="10">
+        <v>5415.77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="E19" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="I19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14">
-        <v>45286</v>
-      </c>
-      <c r="C4" s="14">
-        <v>45296</v>
-      </c>
-      <c r="D4" s="15">
-        <f>C4-B4</f>
-        <v>10</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="12" t="str">
-        <f>RIGHT(E4,2)</f>
-        <v>MG</v>
-      </c>
-      <c r="G4" s="12">
-        <v>1187</v>
-      </c>
-      <c r="H4" s="21">
-        <f>G4/$L$2</f>
-        <v>14.8375</v>
-      </c>
-      <c r="I4" s="12" t="str">
-        <f>TEXT(H4/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos""")</f>
-        <v>00 dias, 14 hora(s), 50 minuto(s), 15 segundos</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="17">
-        <v>2686.67</v>
-      </c>
-      <c r="L4" s="17">
-        <v>7793.19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="14">
-        <v>45286</v>
-      </c>
-      <c r="C5" s="14">
-        <v>45293</v>
-      </c>
-      <c r="D5" s="15">
-        <f>C5-B5</f>
-        <v>7</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="12" t="str">
-        <f>RIGHT(E5,2)</f>
-        <v>SP</v>
-      </c>
-      <c r="G5" s="12">
-        <v>587</v>
-      </c>
-      <c r="H5" s="21">
-        <f t="shared" ref="H5:H12" si="0">G5/$L$2</f>
-        <v>7.3375000000000004</v>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="18">
-        <v>1787.03</v>
-      </c>
-      <c r="L5" s="18">
-        <v>4116.8500000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
-        <v>45289</v>
-      </c>
-      <c r="C6" s="14">
-        <v>45310</v>
-      </c>
-      <c r="D6" s="15">
-        <f t="shared" ref="D6:D12" si="1">C6-B6</f>
-        <v>21</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="12" t="str">
-        <f t="shared" ref="F6:F12" si="2">RIGHT(E6,2)</f>
-        <v>PR</v>
-      </c>
-      <c r="G6" s="12">
-        <v>1457</v>
-      </c>
-      <c r="H6" s="21">
-        <f t="shared" si="0"/>
-        <v>18.212499999999999</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="18">
-        <v>3537.57</v>
-      </c>
-      <c r="L6" s="18">
-        <v>9446.19</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
-        <v>45293</v>
-      </c>
-      <c r="C7" s="14">
-        <v>45317</v>
-      </c>
-      <c r="D7" s="15">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>GO</v>
-      </c>
-      <c r="G7" s="12">
-        <v>1052</v>
-      </c>
-      <c r="H7" s="21">
-        <f t="shared" si="0"/>
-        <v>13.15</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="18">
-        <v>1976.18</v>
-      </c>
-      <c r="L7" s="18">
-        <v>6966.1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
-        <v>45302</v>
-      </c>
-      <c r="C8" s="14">
-        <v>45351</v>
-      </c>
-      <c r="D8" s="15">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>RS</v>
-      </c>
-      <c r="G8" s="12">
-        <v>2909</v>
-      </c>
-      <c r="H8" s="21">
-        <f t="shared" si="0"/>
-        <v>36.362499999999997</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="18">
-        <v>6094.88</v>
-      </c>
-      <c r="L8" s="18">
-        <v>18343.55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14">
-        <v>45303</v>
-      </c>
-      <c r="C9" s="14">
-        <v>45356</v>
-      </c>
-      <c r="D9" s="15">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>PE</v>
-      </c>
-      <c r="G9" s="12">
-        <v>5013</v>
-      </c>
-      <c r="H9" s="21">
-        <f t="shared" si="0"/>
-        <v>62.662500000000001</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="18">
-        <v>8389.85</v>
-      </c>
-      <c r="L9" s="18">
-        <v>31228.11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14">
-        <v>45289</v>
-      </c>
-      <c r="C10" s="14">
-        <v>45309</v>
-      </c>
-      <c r="D10" s="15">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>RJ</v>
-      </c>
-      <c r="G10" s="12">
-        <v>1585</v>
-      </c>
-      <c r="H10" s="21">
-        <f t="shared" si="0"/>
-        <v>19.8125</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="18">
-        <v>4363.38</v>
-      </c>
-      <c r="L10" s="18">
-        <v>10234.4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="14">
-        <v>45301</v>
-      </c>
-      <c r="C11" s="14">
-        <v>45344</v>
-      </c>
-      <c r="D11" s="15">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>BA</v>
-      </c>
-      <c r="G11" s="12">
-        <v>3664</v>
-      </c>
-      <c r="H11" s="21">
-        <f t="shared" si="0"/>
-        <v>45.8</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="18">
-        <v>6500.36</v>
-      </c>
-      <c r="L11" s="18">
-        <v>22963.33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
-        <v>45302</v>
-      </c>
-      <c r="C12" s="14">
-        <v>45349</v>
-      </c>
-      <c r="D12" s="15">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>SP</v>
-      </c>
-      <c r="G12" s="12">
-        <v>799</v>
-      </c>
-      <c r="H12" s="21">
-        <f t="shared" si="0"/>
-        <v>9.9875000000000007</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="18">
-        <v>2406.79</v>
-      </c>
-      <c r="L12" s="18">
-        <v>5415.77</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="E14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="19"/>
-      <c r="I14" s="47" t="s">
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="26"/>
+      <c r="C20" s="27"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="12"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="E21" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="12"/>
+      <c r="I22" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="12"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="34"/>
+      <c r="E25" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="12"/>
+      <c r="I26" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="44"/>
-    </row>
-    <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="20"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="45"/>
-    </row>
-    <row r="16" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-    </row>
-    <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="20"/>
-      <c r="I17" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="44"/>
-    </row>
-    <row r="18" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="45"/>
-    </row>
-    <row r="19" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="E19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-    </row>
-    <row r="20" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="20"/>
-      <c r="I20" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="44"/>
-    </row>
-    <row r="21" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="45"/>
-    </row>
-    <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="E27" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="20"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="E22" s="5" t="s">
+      <c r="C28" s="25"/>
+      <c r="E28" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="19"/>
-    </row>
-    <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="E29" s="40"/>
+    </row>
+    <row r="30" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="31"/>
+      <c r="C30" s="32"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:J3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
@@ -1532,27 +1747,37 @@
       <sortCondition ref="E3"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="16">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
+  <mergeCells count="17">
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="F1:J1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B1:D2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{B72A01B5-D524-4E54-83CF-39C6147C2C75}">
       <formula1>"Guariroba - SP,Jurupema - SP,Taquaritinga - SP,Vila Negri - SP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:C20" xr:uid="{5D55BAFB-7DF3-482B-872A-989542ED9ECE}">
+      <formula1>Destinos</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E20" xr:uid="{F26FBDF0-A241-4428-8D53-DED99D99A8C8}">
+      <formula1>Motoristas</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E29" xr:uid="{026CD0E2-7EB0-4AF1-BB74-206A2FA83D77}">
+      <formula1>Estados</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Exercícios/SigTransp.xlsx
+++ b/Exercícios/SigTransp.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\4. Projetos TIC - Química\ptic_quimica\Exercícios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E95855-05AF-4451-8987-A842C4D64060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027617D9-C41B-410C-9D2C-06E70C447C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
     <sheet name="Transp" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transp!$B$3:$J$3</definedName>
-    <definedName name="Destinos">Transp!$E$4:$E$17</definedName>
-    <definedName name="Estados">Transp!$F$4:$F$17</definedName>
-    <definedName name="Fretes">Transp!$L$4:$L$17</definedName>
-    <definedName name="Motoristas">Transp!$J$4:$J$17</definedName>
+    <definedName name="Destinos">Transp!$E$4:$E$20</definedName>
+    <definedName name="Estados">Transp!$F$4:$F$20</definedName>
+    <definedName name="Fretes">Transp!$L$4:$L$20</definedName>
+    <definedName name="Motoristas">Transp!$J$4:$J$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -185,10 +185,40 @@
     <t>Tempo detalhado (Coluna automática - não mexer)</t>
   </si>
   <si>
-    <t>=SOMASE(Destinos;B20;Fretes)</t>
-  </si>
-  <si>
     <t>=MÉDIA(D4:D17)</t>
+  </si>
+  <si>
+    <t>Palmas - TO</t>
+  </si>
+  <si>
+    <t>Vila Velha - ES</t>
+  </si>
+  <si>
+    <t>Dourados - MS</t>
+  </si>
+  <si>
+    <t>Maria das Cruzes</t>
+  </si>
+  <si>
+    <t>José das Couves</t>
+  </si>
+  <si>
+    <t>João Sai Correndo</t>
+  </si>
+  <si>
+    <t>=SOMASE(Destinos;B23;Fretes)</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>=MÉDIASE(F4:F20;E32;D4:D20)</t>
+  </si>
+  <si>
+    <t>=SOMASES(Fretes;B4:B20;&gt;=B30;c4:c20;&lt;=B32)</t>
+  </si>
+  <si>
+    <t>=SOMASE(Motoristas;E23;Fretes)</t>
   </si>
 </sst>
 </file>
@@ -201,7 +231,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,13 +241,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
@@ -279,13 +302,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Aptos Narrow"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,8 +338,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -533,12 +561,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -552,141 +595,168 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,6 +832,142 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>945173</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>36634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1003789</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Seta: para Cima 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3849DE-0FE2-508E-6AAB-E59905EC491C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2154115" y="6059365"/>
+          <a:ext cx="58616" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>82794</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>90121</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>368544</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>148737</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Seta: para Cima 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5548AA33-A10E-43B2-8984-CFFDF8E65A36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="4717073" y="5772150"/>
+          <a:ext cx="58616" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1084,38 +1290,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
-  <dimension ref="B1:L39"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="3" width="15.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
     <col min="12" max="12" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
       <c r="K1" s="14" t="s">
         <v>36</v>
       </c>
@@ -1124,20 +1330,20 @@
       </c>
     </row>
     <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
       <c r="E2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="29" t="str">
+      <c r="F2" s="35" t="str">
         <f ca="1">"Hoje é "&amp;TEXT(NOW(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa"". Horário: ""hh:mm:ss")</f>
-        <v>Hoje é terça-feira, dia 19 de maio de 2026. Horário: 13:08:23</v>
-      </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+        <v>Hoje é terça-feira, dia 26 de maio de 2026. Horário: 18:38:25</v>
+      </c>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
       <c r="K2" s="17">
         <v>0.61111111111111116</v>
       </c>
@@ -1152,19 +1358,19 @@
       <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="28" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="29" t="s">
         <v>39</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I3" s="16" t="s">
@@ -1188,18 +1394,27 @@
         <f>B4+6</f>
         <v>46371</v>
       </c>
-      <c r="D4" s="49"/>
+      <c r="D4" s="32">
+        <f>C4-B4</f>
+        <v>6</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="50"/>
+      <c r="F4" s="33" t="str">
+        <f>RIGHT(E4,2)</f>
+        <v>MG</v>
+      </c>
       <c r="G4" s="5">
         <v>1187</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="43" t="str">
+      <c r="H4" s="64">
+        <f>G4/$L$2</f>
+        <v>13.188888888888888</v>
+      </c>
+      <c r="I4" s="27" t="str">
         <f>IF(H4&lt;&gt;"",TEXT(H4/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos"""),"")</f>
-        <v/>
+        <v>00 dias, 13 hora(s), 11 minuto(s), 20 segundos</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>12</v>
@@ -1219,18 +1434,27 @@
         <f>B5+7</f>
         <v>46346</v>
       </c>
-      <c r="D5" s="49"/>
+      <c r="D5" s="32">
+        <f t="shared" ref="D5:D20" si="0">C5-B5</f>
+        <v>7</v>
+      </c>
       <c r="E5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="50"/>
+      <c r="F5" s="33" t="str">
+        <f t="shared" ref="F5:F20" si="1">RIGHT(E5,2)</f>
+        <v>SP</v>
+      </c>
       <c r="G5" s="5">
         <v>587</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="43" t="str">
-        <f t="shared" ref="I5:I17" si="0">IF(H5&lt;&gt;"",TEXT(H5/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos"""),"")</f>
-        <v/>
+      <c r="H5" s="64">
+        <f t="shared" ref="H5:H20" si="2">G5/$L$2</f>
+        <v>6.5222222222222221</v>
+      </c>
+      <c r="I5" s="27" t="str">
+        <f t="shared" ref="I5:I20" si="3">IF(H5&lt;&gt;"",TEXT(H5/24,"dd"" dias, ""hh"" hora(s), ""mm"" minuto(s), ""ss"" segundos"""),"")</f>
+        <v>00 dias, 06 hora(s), 31 minuto(s), 20 segundos</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>11</v>
@@ -1250,18 +1474,27 @@
         <f>B6+8</f>
         <v>46366</v>
       </c>
-      <c r="D6" s="49"/>
+      <c r="D6" s="32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="50"/>
+      <c r="F6" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>PE</v>
+      </c>
       <c r="G6" s="5">
         <v>5013</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="H6" s="64">
+        <f t="shared" si="2"/>
+        <v>55.7</v>
+      </c>
+      <c r="I6" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>02 dias, 07 hora(s), 42 minuto(s), 00 segundos</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>17</v>
@@ -1281,18 +1514,27 @@
         <f>B7+9</f>
         <v>46024</v>
       </c>
-      <c r="D7" s="49"/>
+      <c r="D7" s="32">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="50"/>
+      <c r="F7" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>RJ</v>
+      </c>
       <c r="G7" s="5">
         <v>1585</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="H7" s="64">
+        <f t="shared" si="2"/>
+        <v>17.611111111111111</v>
+      </c>
+      <c r="I7" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 17 hora(s), 36 minuto(s), 40 segundos</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>13</v>
@@ -1312,18 +1554,27 @@
         <f>B8+10</f>
         <v>46177</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="32">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="E8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="50"/>
+      <c r="F8" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>BA</v>
+      </c>
       <c r="G8" s="5">
         <v>3664</v>
       </c>
-      <c r="H8" s="51"/>
-      <c r="I8" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="H8" s="64">
+        <f t="shared" si="2"/>
+        <v>40.711111111111109</v>
+      </c>
+      <c r="I8" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 16 hora(s), 42 minuto(s), 40 segundos</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>15</v>
@@ -1343,18 +1594,27 @@
         <f>B9+10</f>
         <v>46335</v>
       </c>
-      <c r="D9" s="49"/>
+      <c r="D9" s="32">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="E9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="50"/>
+      <c r="F9" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>BA</v>
+      </c>
       <c r="G9" s="5">
         <v>3664</v>
       </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="H9" s="64">
+        <f t="shared" si="2"/>
+        <v>40.711111111111109</v>
+      </c>
+      <c r="I9" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 16 hora(s), 42 minuto(s), 40 segundos</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>15</v>
@@ -1367,379 +1627,605 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
-        <v>45982</v>
-      </c>
-      <c r="C10" s="7">
-        <f>B10+9</f>
-        <v>45991</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="5">
-        <v>799</v>
-      </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="43" t="str">
+      <c r="B10" s="49">
+        <v>46114</v>
+      </c>
+      <c r="C10" s="49">
+        <f>B10+5</f>
+        <v>46119</v>
+      </c>
+      <c r="D10" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="10">
-        <v>2406.79</v>
-      </c>
-      <c r="L10" s="10">
-        <v>5415.77</v>
+        <v>5</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>TO</v>
+      </c>
+      <c r="G10" s="52">
+        <v>2820</v>
+      </c>
+      <c r="H10" s="65">
+        <f t="shared" si="2"/>
+        <v>31.333333333333332</v>
+      </c>
+      <c r="I10" s="53" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 07 hora(s), 20 minuto(s), 00 segundos</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="54">
+        <v>7500</v>
+      </c>
+      <c r="L10" s="54">
+        <v>18000</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7">
-        <v>45906</v>
-      </c>
-      <c r="C11" s="7">
-        <f>B11+8</f>
-        <v>45914</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="5">
-        <v>1457</v>
-      </c>
-      <c r="H11" s="51"/>
-      <c r="I11" s="43" t="str">
+      <c r="B11" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="49">
+        <f t="shared" ref="C11:C12" si="4">B11+5</f>
+        <v>46096</v>
+      </c>
+      <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="10">
-        <v>3537.57</v>
-      </c>
-      <c r="L11" s="10">
-        <v>9446.19</v>
+        <v>5</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ES</v>
+      </c>
+      <c r="G11" s="52">
+        <v>2480</v>
+      </c>
+      <c r="H11" s="65">
+        <f t="shared" si="2"/>
+        <v>27.555555555555557</v>
+      </c>
+      <c r="I11" s="53" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 03 hora(s), 33 minuto(s), 20 segundos</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="54">
+        <v>8500</v>
+      </c>
+      <c r="L11" s="54">
+        <v>25000</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
-        <v>45961</v>
-      </c>
-      <c r="C12" s="7">
-        <f>B12+7</f>
-        <v>45968</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="5">
-        <v>1052</v>
-      </c>
-      <c r="H12" s="51"/>
-      <c r="I12" s="43" t="str">
+      <c r="B12" s="49">
+        <v>46047</v>
+      </c>
+      <c r="C12" s="49">
+        <f t="shared" si="4"/>
+        <v>46052</v>
+      </c>
+      <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="10">
-        <v>1976.18</v>
-      </c>
-      <c r="L12" s="10">
-        <v>6966.1</v>
+        <v>5</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>MS</v>
+      </c>
+      <c r="G12" s="52">
+        <v>1624</v>
+      </c>
+      <c r="H12" s="65">
+        <f t="shared" si="2"/>
+        <v>18.044444444444444</v>
+      </c>
+      <c r="I12" s="53" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 18 hora(s), 02 minuto(s), 40 segundos</v>
+      </c>
+      <c r="J12" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="54">
+        <v>9500</v>
+      </c>
+      <c r="L12" s="54">
+        <v>12450</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
-        <v>46166</v>
+        <v>45982</v>
       </c>
       <c r="C13" s="7">
-        <f>B13+6</f>
-        <v>46172</v>
-      </c>
-      <c r="D13" s="49"/>
+        <f>B13+9</f>
+        <v>45991</v>
+      </c>
+      <c r="D13" s="32">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="E13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="50"/>
+        <v>6</v>
+      </c>
+      <c r="F13" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>SP</v>
+      </c>
       <c r="G13" s="5">
-        <v>2909</v>
-      </c>
-      <c r="H13" s="51"/>
-      <c r="I13" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>799</v>
+      </c>
+      <c r="H13" s="64">
+        <f t="shared" si="2"/>
+        <v>8.8777777777777782</v>
+      </c>
+      <c r="I13" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 08 hora(s), 52 minuto(s), 40 segundos</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="10">
-        <v>6094.88</v>
+        <v>2406.79</v>
       </c>
       <c r="L13" s="10">
-        <v>18343.55</v>
+        <v>5415.77</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
-        <v>46065</v>
+        <v>45906</v>
       </c>
       <c r="C14" s="7">
-        <f>B14+5</f>
-        <v>46070</v>
-      </c>
-      <c r="D14" s="49"/>
+        <f>B14+8</f>
+        <v>45914</v>
+      </c>
+      <c r="D14" s="32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="E14" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="50"/>
+        <v>9</v>
+      </c>
+      <c r="F14" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>PR</v>
+      </c>
       <c r="G14" s="5">
-        <v>5013</v>
-      </c>
-      <c r="H14" s="51"/>
-      <c r="I14" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>1457</v>
+      </c>
+      <c r="H14" s="64">
+        <f t="shared" si="2"/>
+        <v>16.18888888888889</v>
+      </c>
+      <c r="I14" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 16 hora(s), 11 minuto(s), 20 segundos</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K14" s="10">
-        <v>8389.85</v>
+        <v>3537.57</v>
       </c>
       <c r="L14" s="10">
-        <v>31228.11</v>
+        <v>9446.19</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="7">
-        <v>45903</v>
+        <v>45961</v>
       </c>
       <c r="C15" s="7">
-        <f>B15+12</f>
-        <v>45915</v>
-      </c>
-      <c r="D15" s="49"/>
+        <f>B15+7</f>
+        <v>45968</v>
+      </c>
+      <c r="D15" s="32">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="E15" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="50"/>
+        <v>8</v>
+      </c>
+      <c r="F15" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>GO</v>
+      </c>
       <c r="G15" s="5">
-        <v>1585</v>
-      </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>1052</v>
+      </c>
+      <c r="H15" s="64">
+        <f t="shared" si="2"/>
+        <v>11.688888888888888</v>
+      </c>
+      <c r="I15" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 11 hora(s), 41 minuto(s), 20 segundos</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="10">
-        <v>4363.38</v>
+        <v>1976.18</v>
       </c>
       <c r="L15" s="10">
-        <v>10234.4</v>
+        <v>6966.1</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
-        <v>46005</v>
+        <v>46166</v>
       </c>
       <c r="C16" s="7">
-        <f>B16+11</f>
-        <v>46016</v>
-      </c>
-      <c r="D16" s="49"/>
+        <f>B16+6</f>
+        <v>46172</v>
+      </c>
+      <c r="D16" s="32">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="E16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="50"/>
+        <v>3</v>
+      </c>
+      <c r="F16" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>RS</v>
+      </c>
       <c r="G16" s="5">
-        <v>3664</v>
-      </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>2909</v>
+      </c>
+      <c r="H16" s="64">
+        <f t="shared" si="2"/>
+        <v>32.322222222222223</v>
+      </c>
+      <c r="I16" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 08 hora(s), 19 minuto(s), 20 segundos</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="10">
-        <v>6500.36</v>
+        <v>6094.88</v>
       </c>
       <c r="L16" s="10">
-        <v>22963.33</v>
+        <v>18343.55</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C17" s="7">
+        <f>B17+5</f>
+        <v>46070</v>
+      </c>
+      <c r="D17" s="32">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>PE</v>
+      </c>
+      <c r="G17" s="5">
+        <v>5013</v>
+      </c>
+      <c r="H17" s="64">
+        <f t="shared" si="2"/>
+        <v>55.7</v>
+      </c>
+      <c r="I17" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>02 dias, 07 hora(s), 42 minuto(s), 00 segundos</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="10">
+        <v>8389.85</v>
+      </c>
+      <c r="L17" s="10">
+        <v>31228.11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C18" s="7">
+        <f>B18+12</f>
+        <v>45915</v>
+      </c>
+      <c r="D18" s="32">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>RJ</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1585</v>
+      </c>
+      <c r="H18" s="64">
+        <f t="shared" si="2"/>
+        <v>17.611111111111111</v>
+      </c>
+      <c r="I18" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 17 hora(s), 36 minuto(s), 40 segundos</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="10">
+        <v>4363.38</v>
+      </c>
+      <c r="L18" s="10">
+        <v>10234.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C19" s="7">
+        <f>B19+11</f>
+        <v>46016</v>
+      </c>
+      <c r="D19" s="32">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>BA</v>
+      </c>
+      <c r="G19" s="5">
+        <v>3664</v>
+      </c>
+      <c r="H19" s="64">
+        <f t="shared" si="2"/>
+        <v>40.711111111111109</v>
+      </c>
+      <c r="I19" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>01 dias, 16 hora(s), 42 minuto(s), 40 segundos</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="10">
+        <v>6500.36</v>
+      </c>
+      <c r="L19" s="10">
+        <v>22963.33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7">
         <v>46144</v>
       </c>
-      <c r="C17" s="7">
-        <f>B17+20</f>
+      <c r="C20" s="7">
+        <f>B20+20</f>
         <v>46164</v>
       </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="8" t="s">
+      <c r="D20" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="5">
+      <c r="F20" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>SP</v>
+      </c>
+      <c r="G20" s="5">
         <v>799</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="H20" s="64">
+        <f t="shared" si="2"/>
+        <v>8.8777777777777782</v>
+      </c>
+      <c r="I20" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>00 dias, 08 hora(s), 52 minuto(s), 40 segundos</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K20" s="10">
         <v>2406.79</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L20" s="10">
         <v>5415.77</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
+    <row r="21" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="E19" s="37" t="s">
+      <c r="C22" s="48"/>
+      <c r="E22" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="I19" s="21" t="s">
+      <c r="F22" s="11"/>
+      <c r="I22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="26"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="12"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="24" t="s">
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="E23" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="E21" s="39" t="s">
+      <c r="C24" s="40"/>
+      <c r="E24" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-    </row>
-    <row r="22" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="12"/>
-      <c r="I22" s="21" t="s">
+      <c r="F24" s="11"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+    </row>
+    <row r="25" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="57">
+        <f>SUMIF(Destinos,B23,Fretes)</f>
+        <v>7793.19</v>
+      </c>
+      <c r="C25" s="58"/>
+      <c r="E25" s="59">
+        <f>SUMIF(Motoristas,E23,Fretes)</f>
+        <v>18000</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="I25" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="47"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="12"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="19"/>
-    </row>
-    <row r="25" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="E25" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-    </row>
-    <row r="26" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="25"/>
-      <c r="E26" s="55"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="E26" s="63" t="s">
+        <v>55</v>
+      </c>
       <c r="F26" s="12"/>
-      <c r="I26" s="21" t="s">
-        <v>42</v>
-      </c>
+      <c r="I26" s="26"/>
       <c r="J26" s="18"/>
     </row>
     <row r="27" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="E27" s="48" t="s">
-        <v>45</v>
-      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
       <c r="I27" s="20"/>
       <c r="J27" s="19"/>
     </row>
-    <row r="28" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="24" t="s">
+    <row r="28" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="38"/>
+      <c r="E28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+    </row>
+    <row r="29" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="E29" s="34">
+        <f>AVERAGE(D4:D20)</f>
+        <v>8.4117647058823533</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="I29" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="61">
+        <v>45962</v>
+      </c>
+      <c r="C30" s="42"/>
+      <c r="E30" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="20"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="E28" s="37" t="s">
+      <c r="C31" s="40"/>
+      <c r="E31" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="11"/>
-    </row>
-    <row r="29" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="E29" s="40"/>
-    </row>
-    <row r="30" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="31"/>
-      <c r="C30" s="32"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="61">
+        <v>46023</v>
+      </c>
+      <c r="C32" s="42"/>
+      <c r="E32" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="55"/>
+      <c r="C33" s="56"/>
+      <c r="E33" s="66">
+        <f>AVERAGEIF(F4:F20,E32,D4:D20)</f>
+        <v>6</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:J3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
@@ -1747,36 +2233,37 @@
       <sortCondition ref="E3"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="17">
+  <mergeCells count="18">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="F1:J1"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H28:J28"/>
     <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{B72A01B5-D524-4E54-83CF-39C6147C2C75}">
       <formula1>"Guariroba - SP,Jurupema - SP,Taquaritinga - SP,Vila Negri - SP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:C20" xr:uid="{5D55BAFB-7DF3-482B-872A-989542ED9ECE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23:C23" xr:uid="{5D55BAFB-7DF3-482B-872A-989542ED9ECE}">
       <formula1>Destinos</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E20" xr:uid="{F26FBDF0-A241-4428-8D53-DED99D99A8C8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23" xr:uid="{F26FBDF0-A241-4428-8D53-DED99D99A8C8}">
       <formula1>Motoristas</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E29" xr:uid="{026CD0E2-7EB0-4AF1-BB74-206A2FA83D77}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E32" xr:uid="{026CD0E2-7EB0-4AF1-BB74-206A2FA83D77}">
       <formula1>Estados</formula1>
     </dataValidation>
   </dataValidations>
